--- a/artfynd/A 59654-2025 artfynd.xlsx
+++ b/artfynd/A 59654-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130328862</v>
       </c>
       <c r="B3" t="n">
-        <v>92950</v>
+        <v>92953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59654-2025 artfynd.xlsx
+++ b/artfynd/A 59654-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130328811</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130328862</v>
       </c>
       <c r="B3" t="n">
-        <v>92953</v>
+        <v>92979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59654-2025 artfynd.xlsx
+++ b/artfynd/A 59654-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130328862</v>
       </c>
       <c r="B3" t="n">
-        <v>92979</v>
+        <v>92980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59654-2025 artfynd.xlsx
+++ b/artfynd/A 59654-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130328862</v>
       </c>
       <c r="B3" t="n">
-        <v>92980</v>
+        <v>92981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59654-2025 artfynd.xlsx
+++ b/artfynd/A 59654-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130328811</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130328862</v>
       </c>
       <c r="B3" t="n">
-        <v>92981</v>
+        <v>92983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59654-2025 artfynd.xlsx
+++ b/artfynd/A 59654-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>130328862</v>
       </c>
       <c r="B3" t="n">
-        <v>92983</v>
+        <v>92987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59654-2025 artfynd.xlsx
+++ b/artfynd/A 59654-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130328811</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130328862</v>
       </c>
       <c r="B3" t="n">
-        <v>92987</v>
+        <v>93000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59654-2025 artfynd.xlsx
+++ b/artfynd/A 59654-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130328811</v>
       </c>
       <c r="B2" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130328862</v>
       </c>
       <c r="B3" t="n">
-        <v>93000</v>
+        <v>93001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59654-2025 artfynd.xlsx
+++ b/artfynd/A 59654-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130328811</v>
       </c>
       <c r="B2" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130328862</v>
       </c>
       <c r="B3" t="n">
-        <v>93001</v>
+        <v>93002</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59654-2025 artfynd.xlsx
+++ b/artfynd/A 59654-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130328811</v>
+        <v>130328862</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>93136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583612</v>
+        <v>583619</v>
       </c>
       <c r="R2" t="n">
-        <v>6423123</v>
+        <v>6423114</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,17 +755,13 @@
           <t>2025-12-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,41 +780,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130328862</v>
+        <v>130328811</v>
       </c>
       <c r="B3" t="n">
-        <v>93002</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2075</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583619</v>
+        <v>583612</v>
       </c>
       <c r="R3" t="n">
-        <v>6423114</v>
+        <v>6423123</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,13 +861,17 @@
           <t>2025-12-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
